--- a/exports/POWERGRID_full_report.xlsx
+++ b/exports/POWERGRID_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>3.4</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>152.2</v>
+        <v>149.45</v>
       </c>
       <c r="I2" t="n">
         <v>150.8685160219102</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K2" t="n">
-        <v>1.91</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
@@ -555,7 +578,7 @@
         <v>0.87</v>
       </c>
       <c r="N2" t="n">
-        <v>2.09</v>
+        <v>2.89</v>
       </c>
       <c r="O2" t="n">
         <v>-0.43</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.73</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44617.55208333334</v>
+        <v>44620.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>144.85</v>
+        <v>150.55</v>
       </c>
       <c r="I3" t="n">
         <v>148.5120033784657</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>3.08</v>
+        <v>-0.74</v>
       </c>
       <c r="L3" t="n">
         <v>1.47</v>
@@ -612,7 +647,7 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>3.13</v>
+        <v>5.38</v>
       </c>
       <c r="O3" t="n">
         <v>-2.89</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.52</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>165.95</v>
+        <v>163.3</v>
       </c>
       <c r="I4" t="n">
         <v>165.4102510205308</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K4" t="n">
-        <v>10.23</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>4.68</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>5.85</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44678.55208333334</v>
+        <v>44679.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>168.75</v>
+        <v>171.85</v>
       </c>
       <c r="I5" t="n">
         <v>171.0548958317988</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.34</v>
+        <v>-5.24</v>
       </c>
       <c r="L5" t="n">
-        <v>4.78</v>
+        <v>5.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.86</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.82</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44698.55208333334</v>
+        <v>44699.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>175.75</v>
+        <v>168.4</v>
       </c>
       <c r="I6" t="n">
         <v>170.9116720473983</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>2.27</v>
+        <v>-2.01</v>
       </c>
       <c r="L6" t="n">
         <v>3.49</v>
@@ -783,7 +854,7 @@
         <v>1.69</v>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>4.78</v>
       </c>
       <c r="O6" t="n">
         <v>2.37</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44750.38541666666</v>
+        <v>44750.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>158.25</v>
+        <v>160.9</v>
       </c>
       <c r="I7" t="n">
         <v>159.0998262352003</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>6.03</v>
+        <v>4.45</v>
       </c>
       <c r="L7" t="n">
         <v>4.01</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>5.87</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44767.38541666666</v>
+        <v>44767.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>152.85</v>
+        <v>152.35</v>
       </c>
       <c r="I8" t="n">
         <v>152.4573006769363</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>-5</v>
+        <v>-5.31</v>
       </c>
       <c r="L8" t="n">
-        <v>5.13</v>
+        <v>5.41</v>
       </c>
       <c r="M8" t="n">
         <v>0.82</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>3.85</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>157.05</v>
+        <v>159.8</v>
       </c>
       <c r="I9" t="n">
         <v>158.2187741977094</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.09</v>
+        <v>-4.89</v>
       </c>
       <c r="L9" t="n">
-        <v>4.89</v>
+        <v>5.09</v>
       </c>
       <c r="M9" t="n">
         <v>0.86</v>
       </c>
       <c r="N9" t="n">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>-1.07</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.62</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44825.38541666666</v>
+        <v>44825.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>168.4</v>
+        <v>164.8</v>
       </c>
       <c r="I10" t="n">
         <v>167.5137914985844</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>5.38</v>
+        <v>3.13</v>
       </c>
       <c r="L10" t="n">
         <v>1.72</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.35</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44834.38541666666</v>
+        <v>44834.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>155.4</v>
+        <v>155.8</v>
       </c>
       <c r="I11" t="n">
         <v>155.7475524938617</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>5.7</v>
+        <v>5.46</v>
       </c>
       <c r="L11" t="n">
         <v>2.79</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.83</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44872.55208333334</v>
+        <v>44874.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>167.45</v>
+        <v>161.95</v>
       </c>
       <c r="I12" t="n">
         <v>163.7016824813604</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>38</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>7.48</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>4.08</v>
@@ -1125,7 +1268,7 @@
         <v>1.29</v>
       </c>
       <c r="N12" t="n">
-        <v>2.48</v>
+        <v>4.12</v>
       </c>
       <c r="O12" t="n">
         <v>2.64</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.19</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>162.85</v>
+        <v>164.05</v>
       </c>
       <c r="I13" t="n">
         <v>163.012890210143</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.3</v>
       </c>
       <c r="L13" t="n">
         <v>4.79</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>3.99</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>157.75</v>
+        <v>156.4</v>
       </c>
       <c r="I14" t="n">
         <v>157.5031567961074</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.84</v>
+        <v>-4.66</v>
       </c>
       <c r="L14" t="n">
-        <v>4.72</v>
+        <v>4.97</v>
       </c>
       <c r="M14" t="n">
         <v>1.35</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.1</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44942.38541666666</v>
+        <v>44942.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>157.6</v>
+        <v>158.2</v>
       </c>
       <c r="I15" t="n">
         <v>157.9783817072082</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>30.83333333333333</v>
+        <v>31</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.77</v>
+        <v>-1.15</v>
       </c>
       <c r="L15" t="n">
         <v>2.85</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>3.63</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44953.55208333334</v>
+        <v>44956.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>160.85</v>
+        <v>154.8</v>
       </c>
       <c r="I16" t="n">
         <v>160.2430559925935</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>1.68</v>
+        <v>-2.15</v>
       </c>
       <c r="L16" t="n">
-        <v>0.73</v>
+        <v>2.31</v>
       </c>
       <c r="M16" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="O16" t="n">
         <v>0.76</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.71</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44984.55208333334</v>
+        <v>44985.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>161.2</v>
+        <v>163</v>
       </c>
       <c r="I17" t="n">
         <v>161.612683763139</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.13</v>
+        <v>-5.3</v>
       </c>
       <c r="L17" t="n">
         <v>6.72</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.33</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45006.38541666666</v>
+        <v>45006.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>163.9</v>
+        <v>163.75</v>
       </c>
       <c r="I18" t="n">
         <v>163.8786160633894</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="L18" t="n">
         <v>2.88</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.73</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45027.38541666666</v>
+        <v>45027.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>168.75</v>
+        <v>169.9</v>
       </c>
       <c r="I19" t="n">
         <v>169.1006045469694</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.05</v>
+        <v>-3.76</v>
       </c>
       <c r="L19" t="n">
         <v>4.09</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.78</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45062.55208333334</v>
+        <v>45063.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>176.5</v>
+        <v>175.55</v>
       </c>
       <c r="I20" t="n">
         <v>176.0800793281622</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>3.88</v>
+        <v>3.33</v>
       </c>
       <c r="L20" t="n">
         <v>1.88</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.58</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45084.55208333334</v>
+        <v>45085.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>176.45</v>
+        <v>179.8</v>
       </c>
       <c r="I21" t="n">
         <v>177.0451884903558</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.51</v>
+        <v>-2.42</v>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
         <v>1.66</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.49</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45114.55208333334</v>
+        <v>45117.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>188.45</v>
+        <v>183.35</v>
       </c>
       <c r="I22" t="n">
         <v>183.7586577341254</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K22" t="n">
-        <v>4.81</v>
+        <v>1.97</v>
       </c>
       <c r="L22" t="n">
         <v>2.17</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>6.75</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>184.75</v>
+        <v>189</v>
       </c>
       <c r="I23" t="n">
         <v>185.8404743631837</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.76</v>
+        <v>-3.08</v>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>4.88</v>
       </c>
       <c r="M23" t="n">
         <v>1.14</v>
       </c>
       <c r="N23" t="n">
-        <v>1.51</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
         <v>-2.28</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.15</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45138.55208333334</v>
+        <v>45139.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>196.45</v>
+        <v>184.8</v>
       </c>
       <c r="I24" t="n">
         <v>185.9429763159257</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.94</v>
+        <v>-2.22</v>
       </c>
       <c r="L24" t="n">
         <v>2.65</v>
       </c>
       <c r="M24" t="n">
-        <v>-0</v>
+        <v>1.78</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
         <v>2.92</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.67</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45166.55208333334</v>
+        <v>45167.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>186.55</v>
+        <v>189.5</v>
       </c>
       <c r="I25" t="n">
         <v>187.7948800010872</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.95</v>
+        <v>-2.54</v>
       </c>
       <c r="L25" t="n">
         <v>4.41</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.75</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>200.2</v>
+        <v>199.5</v>
       </c>
       <c r="I26" t="n">
         <v>199.6047298485906</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>55</v>
+        <v>55.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>5.65</v>
+        <v>5.28</v>
       </c>
       <c r="L26" t="n">
         <v>3.61</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>5.29</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45236.38541666666</v>
+        <v>45236.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>206.55</v>
+        <v>208</v>
       </c>
       <c r="I27" t="n">
         <v>207.4187434102844</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.53</v>
+        <v>-4.26</v>
       </c>
       <c r="L27" t="n">
-        <v>3.88</v>
+        <v>4.74</v>
       </c>
       <c r="M27" t="n">
         <v>0.42</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.8</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>284.95</v>
+        <v>268.45</v>
       </c>
       <c r="I28" t="n">
         <v>276.513375087664</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>127</v>
+        <v>127.8333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>37</v>
+        <v>29.06</v>
       </c>
       <c r="L28" t="n">
         <v>1.11</v>
@@ -2037,7 +2372,7 @@
         <v>4.94</v>
       </c>
       <c r="N28" t="n">
-        <v>4.39</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
         <v>1.84</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45384.38541666666</v>
+        <v>45384.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>278.8</v>
+        <v>279.65</v>
       </c>
       <c r="I29" t="n">
         <v>279.0976845410873</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.86</v>
+        <v>-4.17</v>
       </c>
       <c r="L29" t="n">
         <v>5.76</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.74</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>308.35</v>
+        <v>294.65</v>
       </c>
       <c r="I30" t="n">
         <v>297.9665517238018</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>10.26</v>
+        <v>5.36</v>
       </c>
       <c r="L30" t="n">
         <v>4.02</v>
@@ -2151,7 +2510,7 @@
         <v>1.89</v>
       </c>
       <c r="N30" t="n">
-        <v>2.43</v>
+        <v>4.12</v>
       </c>
       <c r="O30" t="n">
         <v>0.23</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.68</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45427.38541666666</v>
+        <v>45427.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>311.95</v>
+        <v>315</v>
       </c>
       <c r="I31" t="n">
         <v>314.1794357603511</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.87</v>
+        <v>-6.91</v>
       </c>
       <c r="L31" t="n">
-        <v>6.23</v>
+        <v>7.35</v>
       </c>
       <c r="M31" t="n">
         <v>0.52</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.52</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>337.8</v>
+        <v>303.4</v>
       </c>
       <c r="I32" t="n">
         <v>312.7244985285538</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>7.24</v>
+        <v>-3.68</v>
       </c>
       <c r="L32" t="n">
-        <v>3.56</v>
+        <v>11.19</v>
       </c>
       <c r="M32" t="n">
         <v>2.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.49</v>
+        <v>11.19</v>
       </c>
       <c r="O32" t="n">
         <v>1.83</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>15.03</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45464.55208333334</v>
+        <v>45467.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>324.9</v>
+        <v>332.9</v>
       </c>
       <c r="I33" t="n">
         <v>332.7293405726843</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.09</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L33" t="n">
         <v>10.4</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>7.65</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>338.7</v>
+        <v>330.3</v>
       </c>
       <c r="I34" t="n">
         <v>331.2632695408446</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K34" t="n">
-        <v>1.74</v>
+        <v>-0.78</v>
       </c>
       <c r="L34" t="n">
-        <v>3.11</v>
+        <v>3.54</v>
       </c>
       <c r="M34" t="n">
         <v>0.6</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>6.41</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45502.55208333334</v>
+        <v>45503.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>342.85</v>
+        <v>352.9</v>
       </c>
       <c r="I35" t="n">
         <v>351.4687642456613</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.8</v>
+        <v>-6.84</v>
       </c>
       <c r="L35" t="n">
-        <v>4.72</v>
+        <v>8.07</v>
       </c>
       <c r="M35" t="n">
         <v>0.68</v>
       </c>
       <c r="N35" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="O35" t="n">
         <v>-1.24</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>6.92</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45516.55208333334</v>
+        <v>45517.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>340.7</v>
+        <v>338.65</v>
       </c>
       <c r="I36" t="n">
         <v>340.0874925630011</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.46</v>
+        <v>-4.04</v>
       </c>
       <c r="L36" t="n">
-        <v>3.87</v>
+        <v>4.51</v>
       </c>
       <c r="M36" t="n">
         <v>1.36</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.76</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45547.55208333334</v>
+        <v>45548.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>337.2</v>
+        <v>340.95</v>
       </c>
       <c r="I37" t="n">
         <v>339.3125680746497</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K37" t="n">
-        <v>0.43</v>
+        <v>-0.68</v>
       </c>
       <c r="L37" t="n">
         <v>1.37</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>4.44</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>350.7</v>
+        <v>344.4</v>
       </c>
       <c r="I38" t="n">
         <v>345.0799810553365</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="L38" t="n">
         <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>0.74</v>
+        <v>2.2</v>
       </c>
       <c r="N38" t="n">
         <v>2.75</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.7</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>314.5</v>
+        <v>330.9</v>
       </c>
       <c r="I39" t="n">
         <v>327.1163322142256</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K39" t="n">
-        <v>8.68</v>
+        <v>3.92</v>
       </c>
       <c r="L39" t="n">
         <v>1.6</v>
@@ -2664,7 +3131,7 @@
         <v>0.86</v>
       </c>
       <c r="N39" t="n">
-        <v>1.27</v>
+        <v>4.93</v>
       </c>
       <c r="O39" t="n">
         <v>-1.8</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>8.44</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45610.55208333334</v>
+        <v>45614.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>312.1</v>
+        <v>311.7</v>
       </c>
       <c r="I40" t="n">
         <v>311.9570188158295</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.68</v>
+        <v>-5.8</v>
       </c>
       <c r="L40" t="n">
-        <v>6.13</v>
+        <v>6.29</v>
       </c>
       <c r="M40" t="n">
         <v>1.22</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>5.97</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45617.55208333334</v>
+        <v>45618.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>325.3</v>
+        <v>332.8</v>
       </c>
       <c r="I41" t="n">
         <v>328.4080377464323</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.36</v>
+        <v>-6.77</v>
       </c>
       <c r="L41" t="n">
-        <v>4.83</v>
+        <v>6.93</v>
       </c>
       <c r="M41" t="n">
         <v>0.61</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>6.81</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45629.55208333334</v>
+        <v>45630.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>329.9</v>
+        <v>322.5</v>
       </c>
       <c r="I42" t="n">
         <v>322.7282757074085</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.87</v>
+        <v>-3.09</v>
       </c>
       <c r="L42" t="n">
-        <v>2.64</v>
+        <v>3.52</v>
       </c>
       <c r="M42" t="n">
         <v>1.25</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.42</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>298.4</v>
+        <v>304.5</v>
       </c>
       <c r="I43" t="n">
         <v>303.6859150186723</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K43" t="n">
-        <v>7.47</v>
+        <v>5.58</v>
       </c>
       <c r="L43" t="n">
         <v>4.26</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.57</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>296</v>
+        <v>286.05</v>
       </c>
       <c r="I44" t="n">
         <v>291.4813336952357</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.79</v>
+        <v>-6.06</v>
       </c>
       <c r="L44" t="n">
-        <v>3.58</v>
+        <v>6.81</v>
       </c>
       <c r="M44" t="n">
         <v>0.36</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>3.19</v>
       </c>
       <c r="O44" t="n">
         <v>1.59</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>7.39</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>295.9</v>
+        <v>302.85</v>
       </c>
       <c r="I45" t="n">
         <v>302.1999846264982</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.44</v>
+        <v>-5.87</v>
       </c>
       <c r="L45" t="n">
-        <v>3.86</v>
+        <v>5.91</v>
       </c>
       <c r="M45" t="n">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
       <c r="N45" t="n">
         <v>2.56</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.92</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>290.2</v>
+        <v>281.4</v>
       </c>
       <c r="I46" t="n">
         <v>285.6370363155983</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.18</v>
+        <v>-7.08</v>
       </c>
       <c r="L46" t="n">
-        <v>4.69</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M46" t="n">
         <v>0.12</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>254.1</v>
+        <v>266.1</v>
       </c>
       <c r="I47" t="n">
         <v>263.5294774585201</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>9.699999999999999</v>
+        <v>5.44</v>
       </c>
       <c r="L47" t="n">
         <v>3.77</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5</v>
+        <v>1.12</v>
       </c>
       <c r="N47" t="n">
-        <v>2.57</v>
+        <v>4.21</v>
       </c>
       <c r="O47" t="n">
         <v>-1.96</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.71</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45775.55208333334</v>
+        <v>45776.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>308.2</v>
+        <v>301.5</v>
       </c>
       <c r="I48" t="n">
         <v>302.5682409581474</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K48" t="n">
-        <v>15.82</v>
+        <v>13.3</v>
       </c>
       <c r="L48" t="n">
         <v>3.89</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.08</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45817.38541666666</v>
+        <v>45817.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>299.3</v>
+        <v>300.2</v>
       </c>
       <c r="I49" t="n">
         <v>300.0640278743628</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>0.73</v>
+        <v>0.43</v>
       </c>
       <c r="L49" t="n">
         <v>5.27</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>3.72</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>292.7</v>
+        <v>288.7</v>
       </c>
       <c r="I50" t="n">
         <v>290.9404949700609</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.5</v>
+        <v>-3.83</v>
       </c>
       <c r="L50" t="n">
-        <v>2.61</v>
+        <v>3.9</v>
       </c>
       <c r="M50" t="n">
         <v>0.1</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>4.3</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>293.5</v>
+        <v>297.45</v>
       </c>
       <c r="I51" t="n">
         <v>295.486011121865</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.66</v>
+        <v>-3.03</v>
       </c>
       <c r="L51" t="n">
-        <v>2.08</v>
+        <v>3.57</v>
       </c>
       <c r="M51" t="n">
         <v>1.21</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>4.24</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45868.38541666666</v>
+        <v>45868.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I52" t="n">
         <v>291.1998911574444</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.82</v>
+        <v>-2.5</v>
       </c>
       <c r="L52" t="n">
-        <v>2.57</v>
+        <v>3.65</v>
       </c>
       <c r="M52" t="n">
         <v>0.62</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.36</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>279.65</v>
+        <v>287.25</v>
       </c>
       <c r="I53" t="n">
         <v>283.3795160737042</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>3.57</v>
+        <v>0.95</v>
       </c>
       <c r="L53" t="n">
         <v>1.95</v>
@@ -3462,7 +4097,7 @@
         <v>0.74</v>
       </c>
       <c r="N53" t="n">
-        <v>1.33</v>
+        <v>2.27</v>
       </c>
       <c r="O53" t="n">
         <v>-1.02</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.75</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>288.1</v>
+        <v>284.2</v>
       </c>
       <c r="I54" t="n">
         <v>284.9438787252058</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3</v>
+        <v>-1.06</v>
       </c>
       <c r="L54" t="n">
         <v>2.58</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>4.22</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>286.5</v>
+        <v>291.65</v>
       </c>
       <c r="I55" t="n">
         <v>290.8210756355823</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.62</v>
       </c>
       <c r="L55" t="n">
-        <v>2.87</v>
+        <v>3.18</v>
       </c>
       <c r="M55" t="n">
         <v>0.77</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>4.07</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>288</v>
+        <v>279.95</v>
       </c>
       <c r="I56" t="n">
         <v>285.2864150322549</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.25</v>
+        <v>-4.01</v>
       </c>
       <c r="L56" t="n">
-        <v>1.75</v>
+        <v>4.46</v>
       </c>
       <c r="M56" t="n">
-        <v>0.27</v>
+        <v>1.22</v>
       </c>
       <c r="N56" t="n">
-        <v>1.45</v>
+        <v>3.23</v>
       </c>
       <c r="O56" t="n">
         <v>1.62</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.69</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45980.55208333334</v>
+        <v>45981.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>275.2</v>
+        <v>278.15</v>
       </c>
       <c r="I57" t="n">
         <v>277.7212789314672</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K57" t="n">
-        <v>1.7</v>
+        <v>0.64</v>
       </c>
       <c r="L57" t="n">
         <v>1.79</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>3.73</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45992.55208333334</v>
+        <v>45993.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>269.9</v>
+        <v>268.35</v>
       </c>
       <c r="I58" t="n">
         <v>269.2225227852533</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.97</v>
+        <v>-3.52</v>
       </c>
       <c r="L58" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="M58" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="N58" t="n">
         <v>1.44</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>3.4</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>265.1</v>
+        <v>268.2</v>
       </c>
       <c r="I59" t="n">
         <v>265.2702569636315</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>1.21</v>
+        <v>0.06</v>
       </c>
       <c r="L59" t="n">
         <v>1.17</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>4.01</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46021.38541666666</v>
+        <v>46021.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>260.1</v>
+        <v>259.45</v>
       </c>
       <c r="I60" t="n">
         <v>259.4520923960192</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.02</v>
+        <v>-3.26</v>
       </c>
       <c r="L60" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="M60" t="n">
         <v>0.31</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>3.46</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>267.55</v>
+        <v>270.2</v>
       </c>
       <c r="I61" t="n">
         <v>268.4395897110746</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.12</v>
+        <v>-4.14</v>
       </c>
       <c r="L61" t="n">
-        <v>3.12</v>
+        <v>4.88</v>
       </c>
       <c r="M61" t="n">
         <v>0.75</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>3.89</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>264.25</v>
+        <v>258.7</v>
       </c>
       <c r="I62" t="n">
         <v>262.374016645029</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.2</v>
+        <v>-4.26</v>
       </c>
       <c r="L62" t="n">
-        <v>2.5</v>
+        <v>4.29</v>
       </c>
       <c r="M62" t="n">
         <v>1.92</v>
       </c>
       <c r="N62" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="O62" t="n">
         <v>1.35</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>5.41</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055.38541666666</v>
+        <v>46055.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>262.2</v>
+        <v>269.85</v>
       </c>
       <c r="I63" t="n">
         <v>263.4202147306413</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.35</v>
+        <v>-4.31</v>
       </c>
       <c r="L63" t="n">
-        <v>2.55</v>
+        <v>4.83</v>
       </c>
       <c r="M63" t="n">
         <v>1.37</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>295.3</v>
+        <v>293.35</v>
       </c>
       <c r="I64" t="n">
         <v>294.0802572156113</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>28</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>9.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L64" t="n">
         <v>3.32</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>5.18</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46125.55208333334</v>
+        <v>46127.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>300.2</v>
+        <v>311</v>
       </c>
       <c r="I65" t="n">
         <v>306.6985481268742</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.34</v>
+        <v>-6.02</v>
       </c>
       <c r="L65" t="n">
-        <v>5.51</v>
+        <v>6.27</v>
       </c>
       <c r="M65" t="n">
         <v>3.04</v>
       </c>
       <c r="N65" t="n">
-        <v>2.89</v>
+        <v>3.9</v>
       </c>
       <c r="O65" t="n">
         <v>-1.59</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.78</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>309.95</v>
+        <v>306.6</v>
       </c>
       <c r="I66" t="n">
         <v>309.2433795436148</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.34</v>
+        <v>-1.41</v>
       </c>
       <c r="L66" t="n">
         <v>3.14</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.34</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46254.55208333334</v>
+        <v>46255.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>265.2</v>
+        <v>273</v>
       </c>
       <c r="I67" t="n">
         <v>270.6007051048167</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>100</v>
+        <v>100.8333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>13.5</v>
+        <v>10.96</v>
       </c>
       <c r="L67" t="n">
         <v>1.34</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>4.97</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46293.38541666666</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>265.65</v>
+        <v>262.3</v>
       </c>
       <c r="I68" t="n">
         <v>262.7369327128728</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.69</v>
+        <v>-3.92</v>
       </c>
       <c r="L68" t="n">
         <v>4.14</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>39</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7314,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.7</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7324,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7334,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7344,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.6</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46.3</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7374,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7384,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7394,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70.09999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7404,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.41</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7414,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.67</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7434,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>29.06</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7444,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.3</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7454,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.44</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7464,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7474,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.4</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7484,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7494,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7504,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="25">
@@ -6689,7 +7524,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7534,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.66</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7544,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
